--- a/associations_974_la_reunion.xlsx
+++ b/associations_974_la_reunion.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="communes" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'contacts'!$A$1:$H$955</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'contacts'!$A$1:$H$956</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H955"/>
+  <dimension ref="A1:H956"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -35662,28 +35662,32 @@
     <row r="857">
       <c r="A857" t="inlineStr">
         <is>
-          <t>Association Domin Galizé</t>
+          <t>Lalanbik</t>
         </is>
       </c>
       <c r="B857" t="inlineStr">
         <is>
-          <t>Trois-Bassins</t>
+          <t>Saint-Pierre</t>
         </is>
       </c>
       <c r="C857" t="inlineStr">
         <is>
-          <t>domingalize@gmail.com</t>
-        </is>
-      </c>
-      <c r="D857" t="inlineStr"/>
+          <t>info@lalanbik.re</t>
+        </is>
+      </c>
+      <c r="D857" t="inlineStr">
+        <is>
+          <t>06 92 37 89 34</t>
+        </is>
+      </c>
       <c r="E857" t="inlineStr">
         <is>
-          <t>https://docs.trois-bassins.re/associations/Liste-associations-3Bassins.pdf</t>
+          <t>https://www.saintpierre.re/sites/default/files/2023-04/VDS%20123%20V_4.pdf</t>
         </is>
       </c>
       <c r="F857" t="inlineStr">
         <is>
-          <t>2023-11-21 (PDF annuaire des associations de Trois Bassins, MAJ 21/11/2023, docs.trois-bassins.re; site actif 2026)</t>
+          <t>Mars 2023 - magazine municipal La VDS n°123 (PDF publié sur saintpierre.re, avril 2023) : programmation danse du Théâtre de Pierrefonds, ligne 'Réservation : Info@lalanbik.re ou 06 92 37 89 34' ; p.12 cite 'l'association Lalanbik' (convention avec la commune)</t>
         </is>
       </c>
       <c r="G857" t="inlineStr">
@@ -35700,7 +35704,7 @@
     <row r="858">
       <c r="A858" t="inlineStr">
         <is>
-          <t>Association Lo Ker Rényoné</t>
+          <t>Association Domin Galizé</t>
         </is>
       </c>
       <c r="B858" t="inlineStr">
@@ -35710,14 +35714,10 @@
       </c>
       <c r="C858" t="inlineStr">
         <is>
-          <t>laurence.bhiki@gmail.com</t>
-        </is>
-      </c>
-      <c r="D858" t="inlineStr">
-        <is>
-          <t>0692 94 14 59</t>
-        </is>
-      </c>
+          <t>domingalize@gmail.com</t>
+        </is>
+      </c>
+      <c r="D858" t="inlineStr"/>
       <c r="E858" t="inlineStr">
         <is>
           <t>https://docs.trois-bassins.re/associations/Liste-associations-3Bassins.pdf</t>
@@ -35742,7 +35742,7 @@
     <row r="859">
       <c r="A859" t="inlineStr">
         <is>
-          <t>Femmes Actives Manuelles</t>
+          <t>Association Lo Ker Rényoné</t>
         </is>
       </c>
       <c r="B859" t="inlineStr">
@@ -35752,12 +35752,12 @@
       </c>
       <c r="C859" t="inlineStr">
         <is>
-          <t>chamand.mpierre@gmail.com</t>
+          <t>laurence.bhiki@gmail.com</t>
         </is>
       </c>
       <c r="D859" t="inlineStr">
         <is>
-          <t>0692 56 35 29</t>
+          <t>0692 94 14 59</t>
         </is>
       </c>
       <c r="E859" t="inlineStr">
@@ -35784,7 +35784,7 @@
     <row r="860">
       <c r="A860" t="inlineStr">
         <is>
-          <t>Ile en alu</t>
+          <t>Femmes Actives Manuelles</t>
         </is>
       </c>
       <c r="B860" t="inlineStr">
@@ -35794,12 +35794,12 @@
       </c>
       <c r="C860" t="inlineStr">
         <is>
-          <t>pougary.davila@orange.fr</t>
+          <t>chamand.mpierre@gmail.com</t>
         </is>
       </c>
       <c r="D860" t="inlineStr">
         <is>
-          <t>0692 01 24 79</t>
+          <t>0692 56 35 29</t>
         </is>
       </c>
       <c r="E860" t="inlineStr">
@@ -35826,7 +35826,7 @@
     <row r="861">
       <c r="A861" t="inlineStr">
         <is>
-          <t>Mathias Maloya</t>
+          <t>Ile en alu</t>
         </is>
       </c>
       <c r="B861" t="inlineStr">
@@ -35836,12 +35836,12 @@
       </c>
       <c r="C861" t="inlineStr">
         <is>
-          <t>ingridevidot@gmail.com</t>
+          <t>pougary.davila@orange.fr</t>
         </is>
       </c>
       <c r="D861" t="inlineStr">
         <is>
-          <t>0692 19 28 11</t>
+          <t>0692 01 24 79</t>
         </is>
       </c>
       <c r="E861" t="inlineStr">
@@ -35868,7 +35868,7 @@
     <row r="862">
       <c r="A862" t="inlineStr">
         <is>
-          <t>Mélanz à nous</t>
+          <t>Mathias Maloya</t>
         </is>
       </c>
       <c r="B862" t="inlineStr">
@@ -35878,12 +35878,12 @@
       </c>
       <c r="C862" t="inlineStr">
         <is>
-          <t>melanzanou@gmail.com</t>
+          <t>ingridevidot@gmail.com</t>
         </is>
       </c>
       <c r="D862" t="inlineStr">
         <is>
-          <t>0692 51 21 27</t>
+          <t>0692 19 28 11</t>
         </is>
       </c>
       <c r="E862" t="inlineStr">
@@ -35910,7 +35910,7 @@
     <row r="863">
       <c r="A863" t="inlineStr">
         <is>
-          <t>ZOT Y PIN</t>
+          <t>Mélanz à nous</t>
         </is>
       </c>
       <c r="B863" t="inlineStr">
@@ -35920,10 +35920,14 @@
       </c>
       <c r="C863" t="inlineStr">
         <is>
-          <t>clfougeroux@gmail.com</t>
-        </is>
-      </c>
-      <c r="D863" t="inlineStr"/>
+          <t>melanzanou@gmail.com</t>
+        </is>
+      </c>
+      <c r="D863" t="inlineStr">
+        <is>
+          <t>0692 51 21 27</t>
+        </is>
+      </c>
       <c r="E863" t="inlineStr">
         <is>
           <t>https://docs.trois-bassins.re/associations/Liste-associations-3Bassins.pdf</t>
@@ -35948,37 +35952,33 @@
     <row r="864">
       <c r="A864" t="inlineStr">
         <is>
-          <t>A. Dimitile Inter Génération</t>
+          <t>ZOT Y PIN</t>
         </is>
       </c>
       <c r="B864" t="inlineStr">
         <is>
-          <t>Entre-Deux</t>
+          <t>Trois-Bassins</t>
         </is>
       </c>
       <c r="C864" t="inlineStr">
         <is>
-          <t>adig.reunion974@gmail.com</t>
-        </is>
-      </c>
-      <c r="D864" t="inlineStr">
-        <is>
-          <t>0692 48 43 56</t>
-        </is>
-      </c>
+          <t>clfougeroux@gmail.com</t>
+        </is>
+      </c>
+      <c r="D864" t="inlineStr"/>
       <c r="E864" t="inlineStr">
         <is>
-          <t>https://www.entredeux.re/sites/default/files/2023-06/Le%20GUIDE%20des%20associations%20ED-2023.pdf</t>
+          <t>https://docs.trois-bassins.re/associations/Liste-associations-3Bassins.pdf</t>
         </is>
       </c>
       <c r="F864" t="inlineStr">
         <is>
-          <t>2023-06-14 (PDF Guide des associations 2023, publie sur entredeux.re le 14/06/2023)</t>
+          <t>2023-11-21 (PDF annuaire des associations de Trois Bassins, MAJ 21/11/2023, docs.trois-bassins.re; site actif 2026)</t>
         </is>
       </c>
       <c r="G864" t="inlineStr">
         <is>
-          <t>solidarite</t>
+          <t>loisirs_culture</t>
         </is>
       </c>
       <c r="H864" t="inlineStr">
@@ -35990,7 +35990,7 @@
     <row r="865">
       <c r="A865" t="inlineStr">
         <is>
-          <t>AKOZ Association Cultures Océanes Zazakely</t>
+          <t>A. Dimitile Inter Génération</t>
         </is>
       </c>
       <c r="B865" t="inlineStr">
@@ -36000,12 +36000,12 @@
       </c>
       <c r="C865" t="inlineStr">
         <is>
-          <t>asso974.acoz@gmail.com</t>
+          <t>adig.reunion974@gmail.com</t>
         </is>
       </c>
       <c r="D865" t="inlineStr">
         <is>
-          <t>06 92 65 57 39</t>
+          <t>0692 48 43 56</t>
         </is>
       </c>
       <c r="E865" t="inlineStr">
@@ -36032,7 +36032,7 @@
     <row r="866">
       <c r="A866" t="inlineStr">
         <is>
-          <t>JADE Jeune Association pour le Développement Économique et Social</t>
+          <t>AKOZ Association Cultures Océanes Zazakely</t>
         </is>
       </c>
       <c r="B866" t="inlineStr">
@@ -36042,12 +36042,12 @@
       </c>
       <c r="C866" t="inlineStr">
         <is>
-          <t>techer.jade@gmail.com</t>
+          <t>asso974.acoz@gmail.com</t>
         </is>
       </c>
       <c r="D866" t="inlineStr">
         <is>
-          <t>0262 59 99 26</t>
+          <t>06 92 65 57 39</t>
         </is>
       </c>
       <c r="E866" t="inlineStr">
@@ -36074,7 +36074,7 @@
     <row r="867">
       <c r="A867" t="inlineStr">
         <is>
-          <t>Jeunesse Malgache de Demain</t>
+          <t>JADE Jeune Association pour le Développement Économique et Social</t>
         </is>
       </c>
       <c r="B867" t="inlineStr">
@@ -36084,12 +36084,12 @@
       </c>
       <c r="C867" t="inlineStr">
         <is>
-          <t>jcsertier@gmail.com</t>
+          <t>techer.jade@gmail.com</t>
         </is>
       </c>
       <c r="D867" t="inlineStr">
         <is>
-          <t>0692 87 74 32</t>
+          <t>0262 59 99 26</t>
         </is>
       </c>
       <c r="E867" t="inlineStr">
@@ -36116,7 +36116,7 @@
     <row r="868">
       <c r="A868" t="inlineStr">
         <is>
-          <t>Reunis Sourds LFPC</t>
+          <t>Jeunesse Malgache de Demain</t>
         </is>
       </c>
       <c r="B868" t="inlineStr">
@@ -36126,12 +36126,12 @@
       </c>
       <c r="C868" t="inlineStr">
         <is>
-          <t>reunisourdslfpc@gmail.com</t>
+          <t>jcsertier@gmail.com</t>
         </is>
       </c>
       <c r="D868" t="inlineStr">
         <is>
-          <t>0692 10 31 20</t>
+          <t>0692 87 74 32</t>
         </is>
       </c>
       <c r="E868" t="inlineStr">
@@ -36158,7 +36158,7 @@
     <row r="869">
       <c r="A869" t="inlineStr">
         <is>
-          <t>Échange Solidaire Foulpointe Entre-Deux</t>
+          <t>Reunis Sourds LFPC</t>
         </is>
       </c>
       <c r="B869" t="inlineStr">
@@ -36168,12 +36168,12 @@
       </c>
       <c r="C869" t="inlineStr">
         <is>
-          <t>rivierelucien1@gmail.com</t>
+          <t>reunisourdslfpc@gmail.com</t>
         </is>
       </c>
       <c r="D869" t="inlineStr">
         <is>
-          <t>0692 26 52 15</t>
+          <t>0692 10 31 20</t>
         </is>
       </c>
       <c r="E869" t="inlineStr">
@@ -36200,32 +36200,32 @@
     <row r="870">
       <c r="A870" t="inlineStr">
         <is>
-          <t>Alon Feminisme Reunion</t>
+          <t>Échange Solidaire Foulpointe Entre-Deux</t>
         </is>
       </c>
       <c r="B870" t="inlineStr">
         <is>
-          <t>L'Étang-Salé</t>
+          <t>Entre-Deux</t>
         </is>
       </c>
       <c r="C870" t="inlineStr">
         <is>
-          <t>alonfeminismereunion@gmail.com</t>
+          <t>rivierelucien1@gmail.com</t>
         </is>
       </c>
       <c r="D870" t="inlineStr">
         <is>
-          <t>0692.88.15.73</t>
+          <t>0692 26 52 15</t>
         </is>
       </c>
       <c r="E870" t="inlineStr">
         <is>
-          <t>https://www.letangsale.fr/mes-acces-rapides/mes-liens-utiles/annuaire-des-associations?site=2</t>
+          <t>https://www.entredeux.re/sites/default/files/2023-06/Le%20GUIDE%20des%20associations%20ED-2023.pdf</t>
         </is>
       </c>
       <c r="F870" t="inlineStr">
         <is>
-          <t>2026 (annuaire des associations letangsale.fr; site actif: (c) 2026, actualité du 2026-07-07)</t>
+          <t>2023-06-14 (PDF Guide des associations 2023, publie sur entredeux.re le 14/06/2023)</t>
         </is>
       </c>
       <c r="G870" t="inlineStr">
@@ -36235,14 +36235,14 @@
       </c>
       <c r="H870" t="inlineStr">
         <is>
-          <t>site_actif_sans_date</t>
+          <t>date</t>
         </is>
       </c>
     </row>
     <row r="871">
       <c r="A871" t="inlineStr">
         <is>
-          <t>Association Paloma</t>
+          <t>Alon Feminisme Reunion</t>
         </is>
       </c>
       <c r="B871" t="inlineStr">
@@ -36252,17 +36252,17 @@
       </c>
       <c r="C871" t="inlineStr">
         <is>
-          <t>direction@paloma.re</t>
+          <t>alonfeminismereunion@gmail.com</t>
         </is>
       </c>
       <c r="D871" t="inlineStr">
         <is>
-          <t>0692.64.45.54</t>
+          <t>0692.88.15.73</t>
         </is>
       </c>
       <c r="E871" t="inlineStr">
         <is>
-          <t>https://www.letangsale.fr/mes-acces-rapides/mes-liens-utiles/annuaire-des-associations?site=7</t>
+          <t>https://www.letangsale.fr/mes-acces-rapides/mes-liens-utiles/annuaire-des-associations?site=2</t>
         </is>
       </c>
       <c r="F871" t="inlineStr">
@@ -36284,7 +36284,7 @@
     <row r="872">
       <c r="A872" t="inlineStr">
         <is>
-          <t>Bulles A Creer Et Cultiver Le Bonheur</t>
+          <t>Association Paloma</t>
         </is>
       </c>
       <c r="B872" t="inlineStr">
@@ -36294,17 +36294,17 @@
       </c>
       <c r="C872" t="inlineStr">
         <is>
-          <t>bullesacreerlebonheur@gmail.com</t>
+          <t>direction@paloma.re</t>
         </is>
       </c>
       <c r="D872" t="inlineStr">
         <is>
-          <t>0692.05.83.36</t>
+          <t>0692.64.45.54</t>
         </is>
       </c>
       <c r="E872" t="inlineStr">
         <is>
-          <t>https://www.letangsale.fr/mes-acces-rapides/mes-liens-utiles/annuaire-des-associations?site=5</t>
+          <t>https://www.letangsale.fr/mes-acces-rapides/mes-liens-utiles/annuaire-des-associations?site=7</t>
         </is>
       </c>
       <c r="F872" t="inlineStr">
@@ -36326,7 +36326,7 @@
     <row r="873">
       <c r="A873" t="inlineStr">
         <is>
-          <t>Ex Aequo</t>
+          <t>Bulles A Creer Et Cultiver Le Bonheur</t>
         </is>
       </c>
       <c r="B873" t="inlineStr">
@@ -36336,12 +36336,12 @@
       </c>
       <c r="C873" t="inlineStr">
         <is>
-          <t>exaequo.fh@gmail.com</t>
+          <t>bullesacreerlebonheur@gmail.com</t>
         </is>
       </c>
       <c r="D873" t="inlineStr">
         <is>
-          <t>0692.70.52.49</t>
+          <t>0692.05.83.36</t>
         </is>
       </c>
       <c r="E873" t="inlineStr">
@@ -36368,7 +36368,7 @@
     <row r="874">
       <c r="A874" t="inlineStr">
         <is>
-          <t>Les Victimes Silencieuses</t>
+          <t>Ex Aequo</t>
         </is>
       </c>
       <c r="B874" t="inlineStr">
@@ -36378,17 +36378,17 @@
       </c>
       <c r="C874" t="inlineStr">
         <is>
-          <t>victimes.silencieuses@gmail.com</t>
+          <t>exaequo.fh@gmail.com</t>
         </is>
       </c>
       <c r="D874" t="inlineStr">
         <is>
-          <t>0692.28.27.29</t>
+          <t>0692.70.52.49</t>
         </is>
       </c>
       <c r="E874" t="inlineStr">
         <is>
-          <t>https://www.letangsale.fr/mes-acces-rapides/mes-liens-utiles/annuaire-des-associations?site=2</t>
+          <t>https://www.letangsale.fr/mes-acces-rapides/mes-liens-utiles/annuaire-des-associations?site=5</t>
         </is>
       </c>
       <c r="F874" t="inlineStr">
@@ -36410,7 +36410,7 @@
     <row r="875">
       <c r="A875" t="inlineStr">
         <is>
-          <t>Run Odyssea</t>
+          <t>Les Victimes Silencieuses</t>
         </is>
       </c>
       <c r="B875" t="inlineStr">
@@ -36420,17 +36420,17 @@
       </c>
       <c r="C875" t="inlineStr">
         <is>
-          <t>contact@run-odyssea.org</t>
+          <t>victimes.silencieuses@gmail.com</t>
         </is>
       </c>
       <c r="D875" t="inlineStr">
         <is>
-          <t>0693.39.78.05</t>
+          <t>0692.28.27.29</t>
         </is>
       </c>
       <c r="E875" t="inlineStr">
         <is>
-          <t>https://www.letangsale.fr/mes-acces-rapides/mes-liens-utiles/annuaire-des-associations?site=5</t>
+          <t>https://www.letangsale.fr/mes-acces-rapides/mes-liens-utiles/annuaire-des-associations?site=2</t>
         </is>
       </c>
       <c r="F875" t="inlineStr">
@@ -36452,7 +36452,7 @@
     <row r="876">
       <c r="A876" t="inlineStr">
         <is>
-          <t>Saf Ocean Indien</t>
+          <t>Run Odyssea</t>
         </is>
       </c>
       <c r="B876" t="inlineStr">
@@ -36462,17 +36462,17 @@
       </c>
       <c r="C876" t="inlineStr">
         <is>
-          <t>actionsocial.safoi@gmail.com</t>
+          <t>contact@run-odyssea.org</t>
         </is>
       </c>
       <c r="D876" t="inlineStr">
         <is>
-          <t>0692.87.57.87</t>
+          <t>0693.39.78.05</t>
         </is>
       </c>
       <c r="E876" t="inlineStr">
         <is>
-          <t>https://www.letangsale.fr/mes-acces-rapides/mes-liens-utiles/annuaire-des-associations</t>
+          <t>https://www.letangsale.fr/mes-acces-rapides/mes-liens-utiles/annuaire-des-associations?site=5</t>
         </is>
       </c>
       <c r="F876" t="inlineStr">
@@ -36494,28 +36494,32 @@
     <row r="877">
       <c r="A877" t="inlineStr">
         <is>
-          <t>ADACAM 974</t>
+          <t>Saf Ocean Indien</t>
         </is>
       </c>
       <c r="B877" t="inlineStr">
         <is>
-          <t>La Possession</t>
+          <t>L'Étang-Salé</t>
         </is>
       </c>
       <c r="C877" t="inlineStr">
         <is>
-          <t>adacam974@gmail.com</t>
-        </is>
-      </c>
-      <c r="D877" t="inlineStr"/>
+          <t>actionsocial.safoi@gmail.com</t>
+        </is>
+      </c>
+      <c r="D877" t="inlineStr">
+        <is>
+          <t>0692.87.57.87</t>
+        </is>
+      </c>
       <c r="E877" t="inlineStr">
         <is>
-          <t>https://www.lapossession.re/associations/199582</t>
+          <t>https://www.letangsale.fr/mes-acces-rapides/mes-liens-utiles/annuaire-des-associations</t>
         </is>
       </c>
       <c r="F877" t="inlineStr">
         <is>
-          <t>2026 (fiche annuaire des associations lapossession.re; site actif: Copyright 2026, actualités oct. 2026)</t>
+          <t>2026 (annuaire des associations letangsale.fr; site actif: (c) 2026, actualité du 2026-07-07)</t>
         </is>
       </c>
       <c r="G877" t="inlineStr">
@@ -36532,7 +36536,7 @@
     <row r="878">
       <c r="A878" t="inlineStr">
         <is>
-          <t>AHTPAP LOUISE MICHELLE</t>
+          <t>ADACAM 974</t>
         </is>
       </c>
       <c r="B878" t="inlineStr">
@@ -36542,13 +36546,13 @@
       </c>
       <c r="C878" t="inlineStr">
         <is>
-          <t>ahtpap.louisemichelle@gmail.com</t>
+          <t>adacam974@gmail.com</t>
         </is>
       </c>
       <c r="D878" t="inlineStr"/>
       <c r="E878" t="inlineStr">
         <is>
-          <t>https://www.lapossession.re/associations/199600</t>
+          <t>https://www.lapossession.re/associations/199582</t>
         </is>
       </c>
       <c r="F878" t="inlineStr">
@@ -36570,7 +36574,7 @@
     <row r="879">
       <c r="A879" t="inlineStr">
         <is>
-          <t>ARPS ASSOCIATION REUNIONNAISE POUR LA PREVENTION DES RISQUES LIES A LA SEXUALITE</t>
+          <t>AHTPAP LOUISE MICHELLE</t>
         </is>
       </c>
       <c r="B879" t="inlineStr">
@@ -36580,13 +36584,13 @@
       </c>
       <c r="C879" t="inlineStr">
         <is>
-          <t>administration@arps-info.com</t>
+          <t>ahtpap.louisemichelle@gmail.com</t>
         </is>
       </c>
       <c r="D879" t="inlineStr"/>
       <c r="E879" t="inlineStr">
         <is>
-          <t>https://www.lapossession.re/associations/199545</t>
+          <t>https://www.lapossession.re/associations/199600</t>
         </is>
       </c>
       <c r="F879" t="inlineStr">
@@ -36608,7 +36612,7 @@
     <row r="880">
       <c r="A880" t="inlineStr">
         <is>
-          <t>ASSOCIATION ALLONS DEOR</t>
+          <t>ARPS ASSOCIATION REUNIONNAISE POUR LA PREVENTION DES RISQUES LIES A LA SEXUALITE</t>
         </is>
       </c>
       <c r="B880" t="inlineStr">
@@ -36618,13 +36622,13 @@
       </c>
       <c r="C880" t="inlineStr">
         <is>
-          <t>allons.deor@orange.fr</t>
+          <t>administration@arps-info.com</t>
         </is>
       </c>
       <c r="D880" t="inlineStr"/>
       <c r="E880" t="inlineStr">
         <is>
-          <t>https://www.lapossession.re/associations/199585</t>
+          <t>https://www.lapossession.re/associations/199545</t>
         </is>
       </c>
       <c r="F880" t="inlineStr">
@@ -36646,7 +36650,7 @@
     <row r="881">
       <c r="A881" t="inlineStr">
         <is>
-          <t>ASSOCIATION DEPARTEMENTALE HANDICAP MOTEUR DE LA REUNION (ADHMR)</t>
+          <t>ASSOCIATION ALLONS DEOR</t>
         </is>
       </c>
       <c r="B881" t="inlineStr">
@@ -36656,13 +36660,13 @@
       </c>
       <c r="C881" t="inlineStr">
         <is>
-          <t>adhmr974@gmail.com</t>
+          <t>allons.deor@orange.fr</t>
         </is>
       </c>
       <c r="D881" t="inlineStr"/>
       <c r="E881" t="inlineStr">
         <is>
-          <t>https://www.lapossession.re/associations/199564</t>
+          <t>https://www.lapossession.re/associations/199585</t>
         </is>
       </c>
       <c r="F881" t="inlineStr">
@@ -36684,7 +36688,7 @@
     <row r="882">
       <c r="A882" t="inlineStr">
         <is>
-          <t>ASSOCIATION DES DIALYSES ET GREFFES DE LA REUNION</t>
+          <t>ASSOCIATION DEPARTEMENTALE HANDICAP MOTEUR DE LA REUNION (ADHMR)</t>
         </is>
       </c>
       <c r="B882" t="inlineStr">
@@ -36694,13 +36698,13 @@
       </c>
       <c r="C882" t="inlineStr">
         <is>
-          <t>adgreunion@gmail.com</t>
+          <t>adhmr974@gmail.com</t>
         </is>
       </c>
       <c r="D882" t="inlineStr"/>
       <c r="E882" t="inlineStr">
         <is>
-          <t>https://www.lapossession.re/associations/199547</t>
+          <t>https://www.lapossession.re/associations/199564</t>
         </is>
       </c>
       <c r="F882" t="inlineStr">
@@ -36722,7 +36726,7 @@
     <row r="883">
       <c r="A883" t="inlineStr">
         <is>
-          <t>ASSOCIATION FEMMES SOLID'AIR</t>
+          <t>ASSOCIATION DES DIALYSES ET GREFFES DE LA REUNION</t>
         </is>
       </c>
       <c r="B883" t="inlineStr">
@@ -36732,13 +36736,13 @@
       </c>
       <c r="C883" t="inlineStr">
         <is>
-          <t>femmes-solid.air@orange.fr</t>
+          <t>adgreunion@gmail.com</t>
         </is>
       </c>
       <c r="D883" t="inlineStr"/>
       <c r="E883" t="inlineStr">
         <is>
-          <t>https://www.lapossession.re/associations/199592</t>
+          <t>https://www.lapossession.re/associations/199547</t>
         </is>
       </c>
       <c r="F883" t="inlineStr">
@@ -36760,7 +36764,7 @@
     <row r="884">
       <c r="A884" t="inlineStr">
         <is>
-          <t>ASSOCIATION FREDERIC LEVAVASSEUR</t>
+          <t>ASSOCIATION FEMMES SOLID'AIR</t>
         </is>
       </c>
       <c r="B884" t="inlineStr">
@@ -36770,13 +36774,13 @@
       </c>
       <c r="C884" t="inlineStr">
         <is>
-          <t>dlachenaye@afl.re</t>
+          <t>femmes-solid.air@orange.fr</t>
         </is>
       </c>
       <c r="D884" t="inlineStr"/>
       <c r="E884" t="inlineStr">
         <is>
-          <t>https://www.lapossession.re/associations/199561</t>
+          <t>https://www.lapossession.re/associations/199592</t>
         </is>
       </c>
       <c r="F884" t="inlineStr">
@@ -36798,7 +36802,7 @@
     <row r="885">
       <c r="A885" t="inlineStr">
         <is>
-          <t>ASSOCIATION LES AMIS DE L'ECOLE PRIMAIRE PUBLIQUE D'AMBAHITRARAHABA MADAGASCAR</t>
+          <t>ASSOCIATION FREDERIC LEVAVASSEUR</t>
         </is>
       </c>
       <c r="B885" t="inlineStr">
@@ -36808,13 +36812,13 @@
       </c>
       <c r="C885" t="inlineStr">
         <is>
-          <t>stratus.berly@wanadoo.fr</t>
+          <t>dlachenaye@afl.re</t>
         </is>
       </c>
       <c r="D885" t="inlineStr"/>
       <c r="E885" t="inlineStr">
         <is>
-          <t>https://www.lapossession.re/associations/200215</t>
+          <t>https://www.lapossession.re/associations/199561</t>
         </is>
       </c>
       <c r="F885" t="inlineStr">
@@ -36836,7 +36840,7 @@
     <row r="886">
       <c r="A886" t="inlineStr">
         <is>
-          <t>ASSOCIATION RESEAU OTE</t>
+          <t>ASSOCIATION LES AMIS DE L'ECOLE PRIMAIRE PUBLIQUE D'AMBAHITRARAHABA MADAGASCAR</t>
         </is>
       </c>
       <c r="B886" t="inlineStr">
@@ -36846,13 +36850,13 @@
       </c>
       <c r="C886" t="inlineStr">
         <is>
-          <t>reseau.ote@wanadoo.fr</t>
+          <t>stratus.berly@wanadoo.fr</t>
         </is>
       </c>
       <c r="D886" t="inlineStr"/>
       <c r="E886" t="inlineStr">
         <is>
-          <t>https://www.lapossession.re/associations/199598</t>
+          <t>https://www.lapossession.re/associations/200215</t>
         </is>
       </c>
       <c r="F886" t="inlineStr">
@@ -36874,7 +36878,7 @@
     <row r="887">
       <c r="A887" t="inlineStr">
         <is>
-          <t>ASSOCIATION RESEAU VIF</t>
+          <t>ASSOCIATION RESEAU OTE</t>
         </is>
       </c>
       <c r="B887" t="inlineStr">
@@ -36884,13 +36888,13 @@
       </c>
       <c r="C887" t="inlineStr">
         <is>
-          <t>contact@reseauvif.com</t>
+          <t>reseau.ote@wanadoo.fr</t>
         </is>
       </c>
       <c r="D887" t="inlineStr"/>
       <c r="E887" t="inlineStr">
         <is>
-          <t>https://www.lapossession.re/associations/199588</t>
+          <t>https://www.lapossession.re/associations/199598</t>
         </is>
       </c>
       <c r="F887" t="inlineStr">
@@ -36912,7 +36916,7 @@
     <row r="888">
       <c r="A888" t="inlineStr">
         <is>
-          <t>AU TOUR DES BOURGEONS</t>
+          <t>ASSOCIATION RESEAU VIF</t>
         </is>
       </c>
       <c r="B888" t="inlineStr">
@@ -36922,13 +36926,13 @@
       </c>
       <c r="C888" t="inlineStr">
         <is>
-          <t>autourdesbourgeons@gmail.com</t>
+          <t>contact@reseauvif.com</t>
         </is>
       </c>
       <c r="D888" t="inlineStr"/>
       <c r="E888" t="inlineStr">
         <is>
-          <t>https://www.lapossession.re/associations/200231</t>
+          <t>https://www.lapossession.re/associations/199588</t>
         </is>
       </c>
       <c r="F888" t="inlineStr">
@@ -36950,7 +36954,7 @@
     <row r="889">
       <c r="A889" t="inlineStr">
         <is>
-          <t>BELLLS BIEN ETRE, LES LOISIRS &amp; LA SANTÉ</t>
+          <t>AU TOUR DES BOURGEONS</t>
         </is>
       </c>
       <c r="B889" t="inlineStr">
@@ -36960,13 +36964,13 @@
       </c>
       <c r="C889" t="inlineStr">
         <is>
-          <t>mcalogine@yahoo.com</t>
+          <t>autourdesbourgeons@gmail.com</t>
         </is>
       </c>
       <c r="D889" t="inlineStr"/>
       <c r="E889" t="inlineStr">
         <is>
-          <t>https://www.lapossession.re/associations/199557</t>
+          <t>https://www.lapossession.re/associations/200231</t>
         </is>
       </c>
       <c r="F889" t="inlineStr">
@@ -36988,7 +36992,7 @@
     <row r="890">
       <c r="A890" t="inlineStr">
         <is>
-          <t>CLAIRE JOIE</t>
+          <t>BELLLS BIEN ETRE, LES LOISIRS &amp; LA SANTÉ</t>
         </is>
       </c>
       <c r="B890" t="inlineStr">
@@ -36998,13 +37002,13 @@
       </c>
       <c r="C890" t="inlineStr">
         <is>
-          <t>secretariat@clairejoie.re</t>
+          <t>mcalogine@yahoo.com</t>
         </is>
       </c>
       <c r="D890" t="inlineStr"/>
       <c r="E890" t="inlineStr">
         <is>
-          <t>https://www.lapossession.re/associations/199560</t>
+          <t>https://www.lapossession.re/associations/199557</t>
         </is>
       </c>
       <c r="F890" t="inlineStr">
@@ -37026,7 +37030,7 @@
     <row r="891">
       <c r="A891" t="inlineStr">
         <is>
-          <t>COMPAGNON DE JE</t>
+          <t>CLAIRE JOIE</t>
         </is>
       </c>
       <c r="B891" t="inlineStr">
@@ -37036,13 +37040,13 @@
       </c>
       <c r="C891" t="inlineStr">
         <is>
-          <t>c2j@ecomail.re</t>
+          <t>secretariat@clairejoie.re</t>
         </is>
       </c>
       <c r="D891" t="inlineStr"/>
       <c r="E891" t="inlineStr">
         <is>
-          <t>https://www.lapossession.re/associations/199558</t>
+          <t>https://www.lapossession.re/associations/199560</t>
         </is>
       </c>
       <c r="F891" t="inlineStr">
@@ -37064,7 +37068,7 @@
     <row r="892">
       <c r="A892" t="inlineStr">
         <is>
-          <t>COMPAGNONS BATISSEURS DE LA RÉUNION</t>
+          <t>COMPAGNON DE JE</t>
         </is>
       </c>
       <c r="B892" t="inlineStr">
@@ -37074,13 +37078,13 @@
       </c>
       <c r="C892" t="inlineStr">
         <is>
-          <t>s.andoche@compagnonsbatisseurs.eu</t>
+          <t>c2j@ecomail.re</t>
         </is>
       </c>
       <c r="D892" t="inlineStr"/>
       <c r="E892" t="inlineStr">
         <is>
-          <t>https://www.lapossession.re/associations/199584</t>
+          <t>https://www.lapossession.re/associations/199558</t>
         </is>
       </c>
       <c r="F892" t="inlineStr">
@@ -37102,7 +37106,7 @@
     <row r="893">
       <c r="A893" t="inlineStr">
         <is>
-          <t>COPÉRATION RÉGIONALE OCÉAN INDIEN DE SPORT ADAPTÉ</t>
+          <t>COMPAGNONS BATISSEURS DE LA RÉUNION</t>
         </is>
       </c>
       <c r="B893" t="inlineStr">
@@ -37112,13 +37116,13 @@
       </c>
       <c r="C893" t="inlineStr">
         <is>
-          <t>c.r974@wanadoo.fr</t>
+          <t>s.andoche@compagnonsbatisseurs.eu</t>
         </is>
       </c>
       <c r="D893" t="inlineStr"/>
       <c r="E893" t="inlineStr">
         <is>
-          <t>https://www.lapossession.re/associations/199565</t>
+          <t>https://www.lapossession.re/associations/199584</t>
         </is>
       </c>
       <c r="F893" t="inlineStr">
@@ -37140,7 +37144,7 @@
     <row r="894">
       <c r="A894" t="inlineStr">
         <is>
-          <t>CŒUR DE FEMME</t>
+          <t>COPÉRATION RÉGIONALE OCÉAN INDIEN DE SPORT ADAPTÉ</t>
         </is>
       </c>
       <c r="B894" t="inlineStr">
@@ -37150,13 +37154,13 @@
       </c>
       <c r="C894" t="inlineStr">
         <is>
-          <t>coeurdefemme974@gmail.com</t>
+          <t>c.r974@wanadoo.fr</t>
         </is>
       </c>
       <c r="D894" t="inlineStr"/>
       <c r="E894" t="inlineStr">
         <is>
-          <t>https://www.lapossession.re/associations/200232</t>
+          <t>https://www.lapossession.re/associations/199565</t>
         </is>
       </c>
       <c r="F894" t="inlineStr">
@@ -37178,7 +37182,7 @@
     <row r="895">
       <c r="A895" t="inlineStr">
         <is>
-          <t>DEPIST' OUEST</t>
+          <t>CŒUR DE FEMME</t>
         </is>
       </c>
       <c r="B895" t="inlineStr">
@@ -37188,13 +37192,13 @@
       </c>
       <c r="C895" t="inlineStr">
         <is>
-          <t>thore.e@ch-gmartin.fr</t>
+          <t>coeurdefemme974@gmail.com</t>
         </is>
       </c>
       <c r="D895" t="inlineStr"/>
       <c r="E895" t="inlineStr">
         <is>
-          <t>https://www.lapossession.re/associations/199548</t>
+          <t>https://www.lapossession.re/associations/200232</t>
         </is>
       </c>
       <c r="F895" t="inlineStr">
@@ -37216,7 +37220,7 @@
     <row r="896">
       <c r="A896" t="inlineStr">
         <is>
-          <t>ECOL'O DE VIE</t>
+          <t>DEPIST' OUEST</t>
         </is>
       </c>
       <c r="B896" t="inlineStr">
@@ -37226,13 +37230,13 @@
       </c>
       <c r="C896" t="inlineStr">
         <is>
-          <t>ecolodevie@gmail.com</t>
+          <t>thore.e@ch-gmartin.fr</t>
         </is>
       </c>
       <c r="D896" t="inlineStr"/>
       <c r="E896" t="inlineStr">
         <is>
-          <t>https://www.lapossession.re/associations/200227</t>
+          <t>https://www.lapossession.re/associations/199548</t>
         </is>
       </c>
       <c r="F896" t="inlineStr">
@@ -37254,7 +37258,7 @@
     <row r="897">
       <c r="A897" t="inlineStr">
         <is>
-          <t>ED DA LI ZIZ PA LI</t>
+          <t>ECOL'O DE VIE</t>
         </is>
       </c>
       <c r="B897" t="inlineStr">
@@ -37264,13 +37268,13 @@
       </c>
       <c r="C897" t="inlineStr">
         <is>
-          <t>eloisemani441@gmail.com</t>
+          <t>ecolodevie@gmail.com</t>
         </is>
       </c>
       <c r="D897" t="inlineStr"/>
       <c r="E897" t="inlineStr">
         <is>
-          <t>https://www.lapossession.re/associations/200236</t>
+          <t>https://www.lapossession.re/associations/200227</t>
         </is>
       </c>
       <c r="F897" t="inlineStr">
@@ -37292,7 +37296,7 @@
     <row r="898">
       <c r="A898" t="inlineStr">
         <is>
-          <t>FEMMES CONNECTÉES</t>
+          <t>ED DA LI ZIZ PA LI</t>
         </is>
       </c>
       <c r="B898" t="inlineStr">
@@ -37302,13 +37306,13 @@
       </c>
       <c r="C898" t="inlineStr">
         <is>
-          <t>contact.femmesconnectees@gmail.com</t>
+          <t>eloisemani441@gmail.com</t>
         </is>
       </c>
       <c r="D898" t="inlineStr"/>
       <c r="E898" t="inlineStr">
         <is>
-          <t>https://www.lapossession.re/associations/341139</t>
+          <t>https://www.lapossession.re/associations/200236</t>
         </is>
       </c>
       <c r="F898" t="inlineStr">
@@ -37330,7 +37334,7 @@
     <row r="899">
       <c r="A899" t="inlineStr">
         <is>
-          <t>GARD LESPOIR</t>
+          <t>FEMMES CONNECTÉES</t>
         </is>
       </c>
       <c r="B899" t="inlineStr">
@@ -37340,13 +37344,13 @@
       </c>
       <c r="C899" t="inlineStr">
         <is>
-          <t>gardlespoir@hotmail.com</t>
+          <t>contact.femmesconnectees@gmail.com</t>
         </is>
       </c>
       <c r="D899" t="inlineStr"/>
       <c r="E899" t="inlineStr">
         <is>
-          <t>https://www.lapossession.re/associations/199595</t>
+          <t>https://www.lapossession.re/associations/341139</t>
         </is>
       </c>
       <c r="F899" t="inlineStr">
@@ -37368,7 +37372,7 @@
     <row r="900">
       <c r="A900" t="inlineStr">
         <is>
-          <t>GRAMOUNS LE EN LER</t>
+          <t>GARD LESPOIR</t>
         </is>
       </c>
       <c r="B900" t="inlineStr">
@@ -37378,13 +37382,13 @@
       </c>
       <c r="C900" t="inlineStr">
         <is>
-          <t>lesgramouns974@gmail.com</t>
+          <t>gardlespoir@hotmail.com</t>
         </is>
       </c>
       <c r="D900" t="inlineStr"/>
       <c r="E900" t="inlineStr">
         <is>
-          <t>https://www.lapossession.re/associations/199604</t>
+          <t>https://www.lapossession.re/associations/199595</t>
         </is>
       </c>
       <c r="F900" t="inlineStr">
@@ -37406,7 +37410,7 @@
     <row r="901">
       <c r="A901" t="inlineStr">
         <is>
-          <t>HANDI RESILIENCE SOLIDARITE</t>
+          <t>GRAMOUNS LE EN LER</t>
         </is>
       </c>
       <c r="B901" t="inlineStr">
@@ -37416,13 +37420,13 @@
       </c>
       <c r="C901" t="inlineStr">
         <is>
-          <t>handiresol974@gmail.com</t>
+          <t>lesgramouns974@gmail.com</t>
         </is>
       </c>
       <c r="D901" t="inlineStr"/>
       <c r="E901" t="inlineStr">
         <is>
-          <t>https://www.lapossession.re/associations/200239</t>
+          <t>https://www.lapossession.re/associations/199604</t>
         </is>
       </c>
       <c r="F901" t="inlineStr">
@@ -37444,7 +37448,7 @@
     <row r="902">
       <c r="A902" t="inlineStr">
         <is>
-          <t>KADDY SOLIDAIRE</t>
+          <t>HANDI RESILIENCE SOLIDARITE</t>
         </is>
       </c>
       <c r="B902" t="inlineStr">
@@ -37454,13 +37458,13 @@
       </c>
       <c r="C902" t="inlineStr">
         <is>
-          <t>kaddy242426@gmail.com</t>
+          <t>handiresol974@gmail.com</t>
         </is>
       </c>
       <c r="D902" t="inlineStr"/>
       <c r="E902" t="inlineStr">
         <is>
-          <t>https://www.lapossession.re/associations/200216</t>
+          <t>https://www.lapossession.re/associations/200239</t>
         </is>
       </c>
       <c r="F902" t="inlineStr">
@@ -37482,7 +37486,7 @@
     <row r="903">
       <c r="A903" t="inlineStr">
         <is>
-          <t>KER SOLIDAIRE</t>
+          <t>KADDY SOLIDAIRE</t>
         </is>
       </c>
       <c r="B903" t="inlineStr">
@@ -37492,13 +37496,13 @@
       </c>
       <c r="C903" t="inlineStr">
         <is>
-          <t>mariejeannejessica7@gmail.com</t>
+          <t>kaddy242426@gmail.com</t>
         </is>
       </c>
       <c r="D903" t="inlineStr"/>
       <c r="E903" t="inlineStr">
         <is>
-          <t>https://www.lapossession.re/associations/200226</t>
+          <t>https://www.lapossession.re/associations/200216</t>
         </is>
       </c>
       <c r="F903" t="inlineStr">
@@ -37520,7 +37524,7 @@
     <row r="904">
       <c r="A904" t="inlineStr">
         <is>
-          <t>KOUD POUS'</t>
+          <t>KER SOLIDAIRE</t>
         </is>
       </c>
       <c r="B904" t="inlineStr">
@@ -37530,13 +37534,13 @@
       </c>
       <c r="C904" t="inlineStr">
         <is>
-          <t>koudpous974@gmail.com</t>
+          <t>mariejeannejessica7@gmail.com</t>
         </is>
       </c>
       <c r="D904" t="inlineStr"/>
       <c r="E904" t="inlineStr">
         <is>
-          <t>https://www.lapossession.re/associations/200225</t>
+          <t>https://www.lapossession.re/associations/200226</t>
         </is>
       </c>
       <c r="F904" t="inlineStr">
@@ -37558,7 +37562,7 @@
     <row r="905">
       <c r="A905" t="inlineStr">
         <is>
-          <t>KOULER LO KER</t>
+          <t>KOUD POUS'</t>
         </is>
       </c>
       <c r="B905" t="inlineStr">
@@ -37568,13 +37572,13 @@
       </c>
       <c r="C905" t="inlineStr">
         <is>
-          <t>stephane@koulerloker.com</t>
+          <t>koudpous974@gmail.com</t>
         </is>
       </c>
       <c r="D905" t="inlineStr"/>
       <c r="E905" t="inlineStr">
         <is>
-          <t>https://www.lapossession.re/associations/199559</t>
+          <t>https://www.lapossession.re/associations/200225</t>
         </is>
       </c>
       <c r="F905" t="inlineStr">
@@ -37596,7 +37600,7 @@
     <row r="906">
       <c r="A906" t="inlineStr">
         <is>
-          <t>KOZ ANSAMB</t>
+          <t>KOULER LO KER</t>
         </is>
       </c>
       <c r="B906" t="inlineStr">
@@ -37606,13 +37610,13 @@
       </c>
       <c r="C906" t="inlineStr">
         <is>
-          <t>kozansamb974@gmail.com</t>
+          <t>stephane@koulerloker.com</t>
         </is>
       </c>
       <c r="D906" t="inlineStr"/>
       <c r="E906" t="inlineStr">
         <is>
-          <t>https://www.lapossession.re/associations/199602</t>
+          <t>https://www.lapossession.re/associations/199559</t>
         </is>
       </c>
       <c r="F906" t="inlineStr">
@@ -37634,7 +37638,7 @@
     <row r="907">
       <c r="A907" t="inlineStr">
         <is>
-          <t>L'ARBRE A GRANDIR</t>
+          <t>KOZ ANSAMB</t>
         </is>
       </c>
       <c r="B907" t="inlineStr">
@@ -37644,13 +37648,13 @@
       </c>
       <c r="C907" t="inlineStr">
         <is>
-          <t>larbreagrandir@gmail.com</t>
+          <t>kozansamb974@gmail.com</t>
         </is>
       </c>
       <c r="D907" t="inlineStr"/>
       <c r="E907" t="inlineStr">
         <is>
-          <t>https://www.lapossession.re/associations/199578</t>
+          <t>https://www.lapossession.re/associations/199602</t>
         </is>
       </c>
       <c r="F907" t="inlineStr">
@@ -37672,7 +37676,7 @@
     <row r="908">
       <c r="A908" t="inlineStr">
         <is>
-          <t>L'ESSENCE DU LIEN</t>
+          <t>L'ARBRE A GRANDIR</t>
         </is>
       </c>
       <c r="B908" t="inlineStr">
@@ -37682,13 +37686,13 @@
       </c>
       <c r="C908" t="inlineStr">
         <is>
-          <t>lessencedulien@gmail.com</t>
+          <t>larbreagrandir@gmail.com</t>
         </is>
       </c>
       <c r="D908" t="inlineStr"/>
       <c r="E908" t="inlineStr">
         <is>
-          <t>https://www.lapossession.re/associations/199572</t>
+          <t>https://www.lapossession.re/associations/199578</t>
         </is>
       </c>
       <c r="F908" t="inlineStr">
@@ -37710,7 +37714,7 @@
     <row r="909">
       <c r="A909" t="inlineStr">
         <is>
-          <t>LA CAZE DU VIVRE ENSEMBLE</t>
+          <t>L'ESSENCE DU LIEN</t>
         </is>
       </c>
       <c r="B909" t="inlineStr">
@@ -37720,13 +37724,13 @@
       </c>
       <c r="C909" t="inlineStr">
         <is>
-          <t>lacazeduvivreensemble@gmail.com</t>
+          <t>lessencedulien@gmail.com</t>
         </is>
       </c>
       <c r="D909" t="inlineStr"/>
       <c r="E909" t="inlineStr">
         <is>
-          <t>https://www.lapossession.re/associations/200234</t>
+          <t>https://www.lapossession.re/associations/199572</t>
         </is>
       </c>
       <c r="F909" t="inlineStr">
@@ -37748,7 +37752,7 @@
     <row r="910">
       <c r="A910" t="inlineStr">
         <is>
-          <t>LA KAZ JOIE DE VIVRE</t>
+          <t>LA CAZE DU VIVRE ENSEMBLE</t>
         </is>
       </c>
       <c r="B910" t="inlineStr">
@@ -37758,13 +37762,13 @@
       </c>
       <c r="C910" t="inlineStr">
         <is>
-          <t>contact@joiedevivre.re</t>
+          <t>lacazeduvivreensemble@gmail.com</t>
         </is>
       </c>
       <c r="D910" t="inlineStr"/>
       <c r="E910" t="inlineStr">
         <is>
-          <t>https://www.lapossession.re/associations/200233</t>
+          <t>https://www.lapossession.re/associations/200234</t>
         </is>
       </c>
       <c r="F910" t="inlineStr">
@@ -37786,7 +37790,7 @@
     <row r="911">
       <c r="A911" t="inlineStr">
         <is>
-          <t>LA RUE FAMILLE DE FRANCE 974</t>
+          <t>LA KAZ JOIE DE VIVRE</t>
         </is>
       </c>
       <c r="B911" t="inlineStr">
@@ -37796,13 +37800,13 @@
       </c>
       <c r="C911" t="inlineStr">
         <is>
-          <t>antoinearaye@gmail.com</t>
+          <t>contact@joiedevivre.re</t>
         </is>
       </c>
       <c r="D911" t="inlineStr"/>
       <c r="E911" t="inlineStr">
         <is>
-          <t>https://www.lapossession.re/associations/199573</t>
+          <t>https://www.lapossession.re/associations/200233</t>
         </is>
       </c>
       <c r="F911" t="inlineStr">
@@ -37824,7 +37828,7 @@
     <row r="912">
       <c r="A912" t="inlineStr">
         <is>
-          <t>LE COLLECTIF EPA</t>
+          <t>LA RUE FAMILLE DE FRANCE 974</t>
         </is>
       </c>
       <c r="B912" t="inlineStr">
@@ -37834,13 +37838,13 @@
       </c>
       <c r="C912" t="inlineStr">
         <is>
-          <t>lecollectifepa@gmail.com</t>
+          <t>antoinearaye@gmail.com</t>
         </is>
       </c>
       <c r="D912" t="inlineStr"/>
       <c r="E912" t="inlineStr">
         <is>
-          <t>https://www.lapossession.re/associations/199591</t>
+          <t>https://www.lapossession.re/associations/199573</t>
         </is>
       </c>
       <c r="F912" t="inlineStr">
@@ -37862,7 +37866,7 @@
     <row r="913">
       <c r="A913" t="inlineStr">
         <is>
-          <t>LES IRIS</t>
+          <t>LE COLLECTIF EPA</t>
         </is>
       </c>
       <c r="B913" t="inlineStr">
@@ -37872,13 +37876,13 @@
       </c>
       <c r="C913" t="inlineStr">
         <is>
-          <t>associationlesiris@gmail.com</t>
+          <t>lecollectifepa@gmail.com</t>
         </is>
       </c>
       <c r="D913" t="inlineStr"/>
       <c r="E913" t="inlineStr">
         <is>
-          <t>https://www.lapossession.re/associations/200223</t>
+          <t>https://www.lapossession.re/associations/199591</t>
         </is>
       </c>
       <c r="F913" t="inlineStr">
@@ -37900,7 +37904,7 @@
     <row r="914">
       <c r="A914" t="inlineStr">
         <is>
-          <t>LES MALTRAITENCES, MOI J'EN PARLE !</t>
+          <t>LES IRIS</t>
         </is>
       </c>
       <c r="B914" t="inlineStr">
@@ -37910,13 +37914,13 @@
       </c>
       <c r="C914" t="inlineStr">
         <is>
-          <t>nathalie@les-maltraitances-moijenparle.fr</t>
+          <t>associationlesiris@gmail.com</t>
         </is>
       </c>
       <c r="D914" t="inlineStr"/>
       <c r="E914" t="inlineStr">
         <is>
-          <t>https://www.lapossession.re/associations/199590</t>
+          <t>https://www.lapossession.re/associations/200223</t>
         </is>
       </c>
       <c r="F914" t="inlineStr">
@@ -37938,7 +37942,7 @@
     <row r="915">
       <c r="A915" t="inlineStr">
         <is>
-          <t>LUDOKADOK</t>
+          <t>LES MALTRAITENCES, MOI J'EN PARLE !</t>
         </is>
       </c>
       <c r="B915" t="inlineStr">
@@ -37948,13 +37952,13 @@
       </c>
       <c r="C915" t="inlineStr">
         <is>
-          <t>ludokadok.lapossession@gmail.com</t>
+          <t>nathalie@les-maltraitances-moijenparle.fr</t>
         </is>
       </c>
       <c r="D915" t="inlineStr"/>
       <c r="E915" t="inlineStr">
         <is>
-          <t>https://www.lapossession.re/associations/200207</t>
+          <t>https://www.lapossession.re/associations/199590</t>
         </is>
       </c>
       <c r="F915" t="inlineStr">
@@ -37976,7 +37980,7 @@
     <row r="916">
       <c r="A916" t="inlineStr">
         <is>
-          <t>LÉ ENKOR TEMPS</t>
+          <t>LUDOKADOK</t>
         </is>
       </c>
       <c r="B916" t="inlineStr">
@@ -37986,13 +37990,13 @@
       </c>
       <c r="C916" t="inlineStr">
         <is>
-          <t>bonjour@letsgo.re</t>
+          <t>ludokadok.lapossession@gmail.com</t>
         </is>
       </c>
       <c r="D916" t="inlineStr"/>
       <c r="E916" t="inlineStr">
         <is>
-          <t>https://www.lapossession.re/associations/199583</t>
+          <t>https://www.lapossession.re/associations/200207</t>
         </is>
       </c>
       <c r="F916" t="inlineStr">
@@ -38014,7 +38018,7 @@
     <row r="917">
       <c r="A917" t="inlineStr">
         <is>
-          <t>MAISON DU DIABETE</t>
+          <t>LÉ ENKOR TEMPS</t>
         </is>
       </c>
       <c r="B917" t="inlineStr">
@@ -38024,13 +38028,13 @@
       </c>
       <c r="C917" t="inlineStr">
         <is>
-          <t>maisondudiabete974.mdd@gmail.com</t>
+          <t>bonjour@letsgo.re</t>
         </is>
       </c>
       <c r="D917" t="inlineStr"/>
       <c r="E917" t="inlineStr">
         <is>
-          <t>https://www.lapossession.re/associations/199546</t>
+          <t>https://www.lapossession.re/associations/199583</t>
         </is>
       </c>
       <c r="F917" t="inlineStr">
@@ -38052,7 +38056,7 @@
     <row r="918">
       <c r="A918" t="inlineStr">
         <is>
-          <t>OFFRIR UNE GOUTTE D'EAU</t>
+          <t>MAISON DU DIABETE</t>
         </is>
       </c>
       <c r="B918" t="inlineStr">
@@ -38062,13 +38066,13 @@
       </c>
       <c r="C918" t="inlineStr">
         <is>
-          <t>offrirunegouttedeau@outlook.com</t>
+          <t>maisondudiabete974.mdd@gmail.com</t>
         </is>
       </c>
       <c r="D918" t="inlineStr"/>
       <c r="E918" t="inlineStr">
         <is>
-          <t>https://www.lapossession.re/associations/200217</t>
+          <t>https://www.lapossession.re/associations/199546</t>
         </is>
       </c>
       <c r="F918" t="inlineStr">
@@ -38090,7 +38094,7 @@
     <row r="919">
       <c r="A919" t="inlineStr">
         <is>
-          <t>PAIRE 2 CŒURS</t>
+          <t>OFFRIR UNE GOUTTE D'EAU</t>
         </is>
       </c>
       <c r="B919" t="inlineStr">
@@ -38100,13 +38104,13 @@
       </c>
       <c r="C919" t="inlineStr">
         <is>
-          <t>assopaire2coeurs@hotmail.fr</t>
+          <t>offrirunegouttedeau@outlook.com</t>
         </is>
       </c>
       <c r="D919" t="inlineStr"/>
       <c r="E919" t="inlineStr">
         <is>
-          <t>https://www.lapossession.re/associations/200224</t>
+          <t>https://www.lapossession.re/associations/200217</t>
         </is>
       </c>
       <c r="F919" t="inlineStr">
@@ -38128,7 +38132,7 @@
     <row r="920">
       <c r="A920" t="inlineStr">
         <is>
-          <t>REUNION MOELLE ESPOIR</t>
+          <t>PAIRE 2 CŒURS</t>
         </is>
       </c>
       <c r="B920" t="inlineStr">
@@ -38138,13 +38142,13 @@
       </c>
       <c r="C920" t="inlineStr">
         <is>
-          <t>reunionmoelleespoir@gmail.com</t>
+          <t>assopaire2coeurs@hotmail.fr</t>
         </is>
       </c>
       <c r="D920" t="inlineStr"/>
       <c r="E920" t="inlineStr">
         <is>
-          <t>https://www.lapossession.re/associations/199553</t>
+          <t>https://www.lapossession.re/associations/200224</t>
         </is>
       </c>
       <c r="F920" t="inlineStr">
@@ -38166,7 +38170,7 @@
     <row r="921">
       <c r="A921" t="inlineStr">
         <is>
-          <t>SAF OCEAN INDIEN (Syndrome Alcoolisation Fœtale)</t>
+          <t>REUNION MOELLE ESPOIR</t>
         </is>
       </c>
       <c r="B921" t="inlineStr">
@@ -38176,13 +38180,13 @@
       </c>
       <c r="C921" t="inlineStr">
         <is>
-          <t>contactsafoi@gmail.com</t>
+          <t>reunionmoelleespoir@gmail.com</t>
         </is>
       </c>
       <c r="D921" t="inlineStr"/>
       <c r="E921" t="inlineStr">
         <is>
-          <t>https://www.lapossession.re/associations/199551</t>
+          <t>https://www.lapossession.re/associations/199553</t>
         </is>
       </c>
       <c r="F921" t="inlineStr">
@@ -38204,7 +38208,7 @@
     <row r="922">
       <c r="A922" t="inlineStr">
         <is>
-          <t>SAKISOIGNE</t>
+          <t>SAF OCEAN INDIEN (Syndrome Alcoolisation Fœtale)</t>
         </is>
       </c>
       <c r="B922" t="inlineStr">
@@ -38214,17 +38218,13 @@
       </c>
       <c r="C922" t="inlineStr">
         <is>
-          <t>sakisoigne@gmail.com</t>
-        </is>
-      </c>
-      <c r="D922" t="inlineStr">
-        <is>
-          <t>0262 33 42 23</t>
-        </is>
-      </c>
+          <t>contactsafoi@gmail.com</t>
+        </is>
+      </c>
+      <c r="D922" t="inlineStr"/>
       <c r="E922" t="inlineStr">
         <is>
-          <t>https://www.lapossession.re/associations/200237</t>
+          <t>https://www.lapossession.re/associations/199551</t>
         </is>
       </c>
       <c r="F922" t="inlineStr">
@@ -38246,7 +38246,7 @@
     <row r="923">
       <c r="A923" t="inlineStr">
         <is>
-          <t>SAKURA</t>
+          <t>SAKISOIGNE</t>
         </is>
       </c>
       <c r="B923" t="inlineStr">
@@ -38256,13 +38256,17 @@
       </c>
       <c r="C923" t="inlineStr">
         <is>
-          <t>erick@sakura974.re</t>
-        </is>
-      </c>
-      <c r="D923" t="inlineStr"/>
+          <t>sakisoigne@gmail.com</t>
+        </is>
+      </c>
+      <c r="D923" t="inlineStr">
+        <is>
+          <t>0262 33 42 23</t>
+        </is>
+      </c>
       <c r="E923" t="inlineStr">
         <is>
-          <t>https://www.lapossession.re/associations/200241</t>
+          <t>https://www.lapossession.re/associations/200237</t>
         </is>
       </c>
       <c r="F923" t="inlineStr">
@@ -38284,7 +38288,7 @@
     <row r="924">
       <c r="A924" t="inlineStr">
         <is>
-          <t>SOLEY POUR TOUS</t>
+          <t>SAKURA</t>
         </is>
       </c>
       <c r="B924" t="inlineStr">
@@ -38294,13 +38298,13 @@
       </c>
       <c r="C924" t="inlineStr">
         <is>
-          <t>soleypourtous@gmail.com</t>
+          <t>erick@sakura974.re</t>
         </is>
       </c>
       <c r="D924" t="inlineStr"/>
       <c r="E924" t="inlineStr">
         <is>
-          <t>https://www.lapossession.re/associations/200238</t>
+          <t>https://www.lapossession.re/associations/200241</t>
         </is>
       </c>
       <c r="F924" t="inlineStr">
@@ -38322,7 +38326,7 @@
     <row r="925">
       <c r="A925" t="inlineStr">
         <is>
-          <t>SOS GRAMOUNES ISOLÉS</t>
+          <t>SOLEY POUR TOUS</t>
         </is>
       </c>
       <c r="B925" t="inlineStr">
@@ -38332,13 +38336,13 @@
       </c>
       <c r="C925" t="inlineStr">
         <is>
-          <t>louaiselpatrice@gmail.com</t>
+          <t>soleypourtous@gmail.com</t>
         </is>
       </c>
       <c r="D925" t="inlineStr"/>
       <c r="E925" t="inlineStr">
         <is>
-          <t>https://www.lapossession.re/associations/199601</t>
+          <t>https://www.lapossession.re/associations/200238</t>
         </is>
       </c>
       <c r="F925" t="inlineStr">
@@ -38360,7 +38364,7 @@
     <row r="926">
       <c r="A926" t="inlineStr">
         <is>
-          <t>SOS SOLITUDE</t>
+          <t>SOS GRAMOUNES ISOLÉS</t>
         </is>
       </c>
       <c r="B926" t="inlineStr">
@@ -38370,13 +38374,13 @@
       </c>
       <c r="C926" t="inlineStr">
         <is>
-          <t>sossol974@gmail.com</t>
+          <t>louaiselpatrice@gmail.com</t>
         </is>
       </c>
       <c r="D926" t="inlineStr"/>
       <c r="E926" t="inlineStr">
         <is>
-          <t>https://www.lapossession.re/associations/199597</t>
+          <t>https://www.lapossession.re/associations/199601</t>
         </is>
       </c>
       <c r="F926" t="inlineStr">
@@ -38398,7 +38402,7 @@
     <row r="927">
       <c r="A927" t="inlineStr">
         <is>
-          <t>SPECIAL OLYMPICS REUNION</t>
+          <t>SOS SOLITUDE</t>
         </is>
       </c>
       <c r="B927" t="inlineStr">
@@ -38408,13 +38412,13 @@
       </c>
       <c r="C927" t="inlineStr">
         <is>
-          <t>soreunionchair@gmail.com</t>
+          <t>sossol974@gmail.com</t>
         </is>
       </c>
       <c r="D927" t="inlineStr"/>
       <c r="E927" t="inlineStr">
         <is>
-          <t>https://www.lapossession.re/associations/200240</t>
+          <t>https://www.lapossession.re/associations/199597</t>
         </is>
       </c>
       <c r="F927" t="inlineStr">
@@ -38436,7 +38440,7 @@
     <row r="928">
       <c r="A928" t="inlineStr">
         <is>
-          <t>SYNERGIE FAMILIE</t>
+          <t>SPECIAL OLYMPICS REUNION</t>
         </is>
       </c>
       <c r="B928" t="inlineStr">
@@ -38446,13 +38450,13 @@
       </c>
       <c r="C928" t="inlineStr">
         <is>
-          <t>mathilde.roux@synergiefamily.com</t>
+          <t>soreunionchair@gmail.com</t>
         </is>
       </c>
       <c r="D928" t="inlineStr"/>
       <c r="E928" t="inlineStr">
         <is>
-          <t>https://www.lapossession.re/associations/199570</t>
+          <t>https://www.lapossession.re/associations/200240</t>
         </is>
       </c>
       <c r="F928" t="inlineStr">
@@ -38474,7 +38478,7 @@
     <row r="929">
       <c r="A929" t="inlineStr">
         <is>
-          <t>TU ES MON AUTRE</t>
+          <t>SYNERGIE FAMILIE</t>
         </is>
       </c>
       <c r="B929" t="inlineStr">
@@ -38484,13 +38488,13 @@
       </c>
       <c r="C929" t="inlineStr">
         <is>
-          <t>asso.tuesmonautre@gmail.com</t>
+          <t>mathilde.roux@synergiefamily.com</t>
         </is>
       </c>
       <c r="D929" t="inlineStr"/>
       <c r="E929" t="inlineStr">
         <is>
-          <t>https://www.lapossession.re/associations/200218</t>
+          <t>https://www.lapossession.re/associations/199570</t>
         </is>
       </c>
       <c r="F929" t="inlineStr">
@@ -38512,7 +38516,7 @@
     <row r="930">
       <c r="A930" t="inlineStr">
         <is>
-          <t>UN AVENIR POUR TOUS</t>
+          <t>TU ES MON AUTRE</t>
         </is>
       </c>
       <c r="B930" t="inlineStr">
@@ -38522,13 +38526,13 @@
       </c>
       <c r="C930" t="inlineStr">
         <is>
-          <t>mireille.chungchin@gmail.com</t>
+          <t>asso.tuesmonautre@gmail.com</t>
         </is>
       </c>
       <c r="D930" t="inlineStr"/>
       <c r="E930" t="inlineStr">
         <is>
-          <t>https://www.lapossession.re/associations/200229</t>
+          <t>https://www.lapossession.re/associations/200218</t>
         </is>
       </c>
       <c r="F930" t="inlineStr">
@@ -38550,7 +38554,7 @@
     <row r="931">
       <c r="A931" t="inlineStr">
         <is>
-          <t>UN CŒUR C'EST UN CŒUR</t>
+          <t>UN AVENIR POUR TOUS</t>
         </is>
       </c>
       <c r="B931" t="inlineStr">
@@ -38560,13 +38564,13 @@
       </c>
       <c r="C931" t="inlineStr">
         <is>
-          <t>fabrice@uncoeurcestuncoeur.re</t>
+          <t>mireille.chungchin@gmail.com</t>
         </is>
       </c>
       <c r="D931" t="inlineStr"/>
       <c r="E931" t="inlineStr">
         <is>
-          <t>https://www.lapossession.re/associations/200228</t>
+          <t>https://www.lapossession.re/associations/200229</t>
         </is>
       </c>
       <c r="F931" t="inlineStr">
@@ -38588,7 +38592,7 @@
     <row r="932">
       <c r="A932" t="inlineStr">
         <is>
-          <t>UN FRUIT DE LA PASSION</t>
+          <t>UN CŒUR C'EST UN CŒUR</t>
         </is>
       </c>
       <c r="B932" t="inlineStr">
@@ -38598,13 +38602,13 @@
       </c>
       <c r="C932" t="inlineStr">
         <is>
-          <t>unfruitdelapassion974@gmail.com</t>
+          <t>fabrice@uncoeurcestuncoeur.re</t>
         </is>
       </c>
       <c r="D932" t="inlineStr"/>
       <c r="E932" t="inlineStr">
         <is>
-          <t>https://www.lapossession.re/associations/200230</t>
+          <t>https://www.lapossession.re/associations/200228</t>
         </is>
       </c>
       <c r="F932" t="inlineStr">
@@ -38626,7 +38630,7 @@
     <row r="933">
       <c r="A933" t="inlineStr">
         <is>
-          <t>VIVRE AVEC LE S.A.F</t>
+          <t>UN FRUIT DE LA PASSION</t>
         </is>
       </c>
       <c r="B933" t="inlineStr">
@@ -38636,13 +38640,13 @@
       </c>
       <c r="C933" t="inlineStr">
         <is>
-          <t>vivreaveclesaf.oi@gmail.com</t>
+          <t>unfruitdelapassion974@gmail.com</t>
         </is>
       </c>
       <c r="D933" t="inlineStr"/>
       <c r="E933" t="inlineStr">
         <is>
-          <t>https://www.lapossession.re/associations/199552</t>
+          <t>https://www.lapossession.re/associations/200230</t>
         </is>
       </c>
       <c r="F933" t="inlineStr">
@@ -38664,32 +38668,28 @@
     <row r="934">
       <c r="A934" t="inlineStr">
         <is>
-          <t>Association Liaison</t>
+          <t>VIVRE AVEC LE S.A.F</t>
         </is>
       </c>
       <c r="B934" t="inlineStr">
         <is>
-          <t>Le Port</t>
+          <t>La Possession</t>
         </is>
       </c>
       <c r="C934" t="inlineStr">
         <is>
-          <t>liaison.association@hotmail.fr</t>
-        </is>
-      </c>
-      <c r="D934" t="inlineStr">
-        <is>
-          <t>0262 43 16 15</t>
-        </is>
-      </c>
+          <t>vivreaveclesaf.oi@gmail.com</t>
+        </is>
+      </c>
+      <c r="D934" t="inlineStr"/>
       <c r="E934" t="inlineStr">
         <is>
-          <t>https://www.ville-port.re/annuaire-des-clubs-sportifs-2/</t>
+          <t>https://www.lapossession.re/associations/199552</t>
         </is>
       </c>
       <c r="F934" t="inlineStr">
         <is>
-          <t>2026 (annuaire des associations sportives portoises 2026/2027, page ville-port.re)</t>
+          <t>2026 (fiche annuaire des associations lapossession.re; site actif: Copyright 2026, actualités oct. 2026)</t>
         </is>
       </c>
       <c r="G934" t="inlineStr">
@@ -38699,14 +38699,14 @@
       </c>
       <c r="H934" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>site_actif_sans_date</t>
         </is>
       </c>
     </row>
     <row r="935">
       <c r="A935" t="inlineStr">
         <is>
-          <t>Association Prévention Éducation Recherche Formation REED</t>
+          <t>Association Liaison</t>
         </is>
       </c>
       <c r="B935" t="inlineStr">
@@ -38716,12 +38716,12 @@
       </c>
       <c r="C935" t="inlineStr">
         <is>
-          <t>sec.aperf974@gmail.com</t>
+          <t>liaison.association@hotmail.fr</t>
         </is>
       </c>
       <c r="D935" t="inlineStr">
         <is>
-          <t>0692 68 34 34</t>
+          <t>0262 43 16 15</t>
         </is>
       </c>
       <c r="E935" t="inlineStr">
@@ -38748,32 +38748,32 @@
     <row r="936">
       <c r="A936" t="inlineStr">
         <is>
-          <t>Refuge Ti Lou (protection animale)</t>
+          <t>Association Prévention Éducation Recherche Formation REED</t>
         </is>
       </c>
       <c r="B936" t="inlineStr">
         <is>
-          <t>Le Tampon</t>
+          <t>Le Port</t>
         </is>
       </c>
       <c r="C936" t="inlineStr">
         <is>
-          <t>contact@tilou.re</t>
+          <t>sec.aperf974@gmail.com</t>
         </is>
       </c>
       <c r="D936" t="inlineStr">
         <is>
-          <t>09 76 31 68 99</t>
+          <t>0692 68 34 34</t>
         </is>
       </c>
       <c r="E936" t="inlineStr">
         <is>
-          <t>https://letampon.fr/wp-content/uploads/2026/02/Tampon-magazine-68-mars-2026.pdf</t>
+          <t>https://www.ville-port.re/annuaire-des-clubs-sportifs-2/</t>
         </is>
       </c>
       <c r="F936" t="inlineStr">
         <is>
-          <t>2026-03 (PDF Tampon Magazine n°68, mars 2026)</t>
+          <t>2026 (annuaire des associations sportives portoises 2026/2027, page ville-port.re)</t>
         </is>
       </c>
       <c r="G936" t="inlineStr">
@@ -38790,32 +38790,32 @@
     <row r="937">
       <c r="A937" t="inlineStr">
         <is>
-          <t>Des Aidants et des Aidés 974 (AAA 974)</t>
+          <t>Refuge Ti Lou (protection animale)</t>
         </is>
       </c>
       <c r="B937" t="inlineStr">
         <is>
-          <t>Petite-Île</t>
+          <t>Le Tampon</t>
         </is>
       </c>
       <c r="C937" t="inlineStr">
         <is>
-          <t>associationaaa974@gmail.com</t>
+          <t>contact@tilou.re</t>
         </is>
       </c>
       <c r="D937" t="inlineStr">
         <is>
-          <t>0692 52 44 81</t>
+          <t>09 76 31 68 99</t>
         </is>
       </c>
       <c r="E937" t="inlineStr">
         <is>
-          <t>https://www.petite-ile.re/ma-ville/associations</t>
+          <t>https://letampon.fr/wp-content/uploads/2026/02/Tampon-magazine-68-mars-2026.pdf</t>
         </is>
       </c>
       <c r="F937" t="inlineStr">
         <is>
-          <t>2026 - annuaire en ligne de la mairie (pages ?page=0 a 9), non date par page ; site mairie actif (bulletins sanitaires jusqu'a sept. 2026, copyright 2026)</t>
+          <t>2026-03 (PDF Tampon Magazine n°68, mars 2026)</t>
         </is>
       </c>
       <c r="G937" t="inlineStr">
@@ -38825,14 +38825,14 @@
       </c>
       <c r="H937" t="inlineStr">
         <is>
-          <t>site_actif_sans_date</t>
+          <t>date</t>
         </is>
       </c>
     </row>
     <row r="938">
       <c r="A938" t="inlineStr">
         <is>
-          <t>Développement d'Actions Sociales et Environnementales (ADASE)</t>
+          <t>Des Aidants et des Aidés 974 (AAA 974)</t>
         </is>
       </c>
       <c r="B938" t="inlineStr">
@@ -38842,12 +38842,12 @@
       </c>
       <c r="C938" t="inlineStr">
         <is>
-          <t>danielbriandy@orange.fr</t>
+          <t>associationaaa974@gmail.com</t>
         </is>
       </c>
       <c r="D938" t="inlineStr">
         <is>
-          <t>0692 87 56 42 - 0692 87 72 88</t>
+          <t>0692 52 44 81</t>
         </is>
       </c>
       <c r="E938" t="inlineStr">
@@ -38874,7 +38874,7 @@
     <row r="939">
       <c r="A939" t="inlineStr">
         <is>
-          <t>Hilaros</t>
+          <t>Développement d'Actions Sociales et Environnementales (ADASE)</t>
         </is>
       </c>
       <c r="B939" t="inlineStr">
@@ -38884,12 +38884,12 @@
       </c>
       <c r="C939" t="inlineStr">
         <is>
-          <t>hilaros974@gmail.com</t>
+          <t>danielbriandy@orange.fr</t>
         </is>
       </c>
       <c r="D939" t="inlineStr">
         <is>
-          <t>0692 28 45 72</t>
+          <t>0692 87 56 42 - 0692 87 72 88</t>
         </is>
       </c>
       <c r="E939" t="inlineStr">
@@ -38916,7 +38916,7 @@
     <row r="940">
       <c r="A940" t="inlineStr">
         <is>
-          <t>Kalbass</t>
+          <t>Hilaros</t>
         </is>
       </c>
       <c r="B940" t="inlineStr">
@@ -38926,12 +38926,12 @@
       </c>
       <c r="C940" t="inlineStr">
         <is>
-          <t>kalbass97429@gmail.com</t>
+          <t>hilaros974@gmail.com</t>
         </is>
       </c>
       <c r="D940" t="inlineStr">
         <is>
-          <t>0693 50 02 35</t>
+          <t>0692 28 45 72</t>
         </is>
       </c>
       <c r="E940" t="inlineStr">
@@ -38958,7 +38958,7 @@
     <row r="941">
       <c r="A941" t="inlineStr">
         <is>
-          <t>Kréation pour l'Accompagnement Local des Ouvriers Unis (KALOU)</t>
+          <t>Kalbass</t>
         </is>
       </c>
       <c r="B941" t="inlineStr">
@@ -38968,12 +38968,12 @@
       </c>
       <c r="C941" t="inlineStr">
         <is>
-          <t>associationkalou@gmail.com</t>
+          <t>kalbass97429@gmail.com</t>
         </is>
       </c>
       <c r="D941" t="inlineStr">
         <is>
-          <t>0693 49 92 77</t>
+          <t>0693 50 02 35</t>
         </is>
       </c>
       <c r="E941" t="inlineStr">
@@ -39000,7 +39000,7 @@
     <row r="942">
       <c r="A942" t="inlineStr">
         <is>
-          <t>La Recyclerie du Sud</t>
+          <t>Kréation pour l'Accompagnement Local des Ouvriers Unis (KALOU)</t>
         </is>
       </c>
       <c r="B942" t="inlineStr">
@@ -39010,12 +39010,12 @@
       </c>
       <c r="C942" t="inlineStr">
         <is>
-          <t>pina.celine@yahoo.fr</t>
+          <t>associationkalou@gmail.com</t>
         </is>
       </c>
       <c r="D942" t="inlineStr">
         <is>
-          <t>0692 23 15 20</t>
+          <t>0693 49 92 77</t>
         </is>
       </c>
       <c r="E942" t="inlineStr">
@@ -39042,7 +39042,7 @@
     <row r="943">
       <c r="A943" t="inlineStr">
         <is>
-          <t>Les Samaritains</t>
+          <t>La Recyclerie du Sud</t>
         </is>
       </c>
       <c r="B943" t="inlineStr">
@@ -39052,12 +39052,12 @@
       </c>
       <c r="C943" t="inlineStr">
         <is>
-          <t>fredgigan97410@gmail.com</t>
+          <t>pina.celine@yahoo.fr</t>
         </is>
       </c>
       <c r="D943" t="inlineStr">
         <is>
-          <t>0693 94 62 55</t>
+          <t>0692 23 15 20</t>
         </is>
       </c>
       <c r="E943" t="inlineStr">
@@ -39084,7 +39084,7 @@
     <row r="944">
       <c r="A944" t="inlineStr">
         <is>
-          <t>Mouvement lé bon (MLB)</t>
+          <t>Les Samaritains</t>
         </is>
       </c>
       <c r="B944" t="inlineStr">
@@ -39094,12 +39094,12 @@
       </c>
       <c r="C944" t="inlineStr">
         <is>
-          <t>moutoussamvalfredine@gmail.com</t>
+          <t>fredgigan97410@gmail.com</t>
         </is>
       </c>
       <c r="D944" t="inlineStr">
         <is>
-          <t>0692 57 63 12</t>
+          <t>0693 94 62 55</t>
         </is>
       </c>
       <c r="E944" t="inlineStr">
@@ -39126,7 +39126,7 @@
     <row r="945">
       <c r="A945" t="inlineStr">
         <is>
-          <t>Médiation Familiale Sud Sauvage (AMF2S)</t>
+          <t>Mouvement lé bon (MLB)</t>
         </is>
       </c>
       <c r="B945" t="inlineStr">
@@ -39136,12 +39136,12 @@
       </c>
       <c r="C945" t="inlineStr">
         <is>
-          <t>asso.mf2s@gmail.com</t>
+          <t>moutoussamvalfredine@gmail.com</t>
         </is>
       </c>
       <c r="D945" t="inlineStr">
         <is>
-          <t>0262 30 68 50 - 0692 28 52 11</t>
+          <t>0692 57 63 12</t>
         </is>
       </c>
       <c r="E945" t="inlineStr">
@@ -39168,7 +39168,7 @@
     <row r="946">
       <c r="A946" t="inlineStr">
         <is>
-          <t>Un Geste, Un Sourire</t>
+          <t>Médiation Familiale Sud Sauvage (AMF2S)</t>
         </is>
       </c>
       <c r="B946" t="inlineStr">
@@ -39178,12 +39178,12 @@
       </c>
       <c r="C946" t="inlineStr">
         <is>
-          <t>ungesteunsourire@mailfence.com</t>
+          <t>asso.mf2s@gmail.com</t>
         </is>
       </c>
       <c r="D946" t="inlineStr">
         <is>
-          <t>0692 94 69 16</t>
+          <t>0262 30 68 50 - 0692 28 52 11</t>
         </is>
       </c>
       <c r="E946" t="inlineStr">
@@ -39210,7 +39210,7 @@
     <row r="947">
       <c r="A947" t="inlineStr">
         <is>
-          <t>Vivons Petite-Île</t>
+          <t>Un Geste, Un Sourire</t>
         </is>
       </c>
       <c r="B947" t="inlineStr">
@@ -39220,12 +39220,12 @@
       </c>
       <c r="C947" t="inlineStr">
         <is>
-          <t>gonthierfrederic8@gmail.com</t>
+          <t>ungesteunsourire@mailfence.com</t>
         </is>
       </c>
       <c r="D947" t="inlineStr">
         <is>
-          <t>0692 62 69 80</t>
+          <t>0692 94 69 16</t>
         </is>
       </c>
       <c r="E947" t="inlineStr">
@@ -39252,32 +39252,32 @@
     <row r="948">
       <c r="A948" t="inlineStr">
         <is>
-          <t>Association féminine de l'Est contre tristesse, tyrannie, traumatisme (AFECTTT)</t>
+          <t>Vivons Petite-Île</t>
         </is>
       </c>
       <c r="B948" t="inlineStr">
         <is>
-          <t>Saint-Benoît</t>
+          <t>Petite-Île</t>
         </is>
       </c>
       <c r="C948" t="inlineStr">
         <is>
-          <t>afecttt3@orange.fr</t>
+          <t>gonthierfrederic8@gmail.com</t>
         </is>
       </c>
       <c r="D948" t="inlineStr">
         <is>
-          <t>0692 61 76 59</t>
+          <t>0692 62 69 80</t>
         </is>
       </c>
       <c r="E948" t="inlineStr">
         <is>
-          <t>https://www.saint-benoit.re/page/475-associations-daction-sociale-humanitaire-entraide</t>
+          <t>https://www.petite-ile.re/ma-ville/associations</t>
         </is>
       </c>
       <c r="F948" t="inlineStr">
         <is>
-          <t>Page mairie non datée ; site mairie actif (actualités publiées 2026-10-19, rubrique Rouge Ruelle 2026), relevé 2026-10-20</t>
+          <t>2026 - annuaire en ligne de la mairie (pages ?page=0 a 9), non date par page ; site mairie actif (bulletins sanitaires jusqu'a sept. 2026, copyright 2026)</t>
         </is>
       </c>
       <c r="G948" t="inlineStr">
@@ -39294,7 +39294,7 @@
     <row r="949">
       <c r="A949" t="inlineStr">
         <is>
-          <t>Épi-Est</t>
+          <t>Association féminine de l'Est contre tristesse, tyrannie, traumatisme (AFECTTT)</t>
         </is>
       </c>
       <c r="B949" t="inlineStr">
@@ -39304,17 +39304,17 @@
       </c>
       <c r="C949" t="inlineStr">
         <is>
-          <t>epi.est@sfr.fr</t>
+          <t>afecttt3@orange.fr</t>
         </is>
       </c>
       <c r="D949" t="inlineStr">
         <is>
-          <t>0692 86 33 46</t>
+          <t>0692 61 76 59</t>
         </is>
       </c>
       <c r="E949" t="inlineStr">
         <is>
-          <t>https://www.saint-benoit.re/page/483-associations-de-linsertion</t>
+          <t>https://www.saint-benoit.re/page/475-associations-daction-sociale-humanitaire-entraide</t>
         </is>
       </c>
       <c r="F949" t="inlineStr">
@@ -39336,32 +39336,32 @@
     <row r="950">
       <c r="A950" t="inlineStr">
         <is>
-          <t>Psychez Toi</t>
+          <t>Épi-Est</t>
         </is>
       </c>
       <c r="B950" t="inlineStr">
         <is>
-          <t>Saint-Leu</t>
+          <t>Saint-Benoît</t>
         </is>
       </c>
       <c r="C950" t="inlineStr">
         <is>
-          <t>psycheztoi@gmail.com</t>
+          <t>epi.est@sfr.fr</t>
         </is>
       </c>
       <c r="D950" t="inlineStr">
         <is>
-          <t>06 93 92 04 23</t>
+          <t>0692 86 33 46</t>
         </is>
       </c>
       <c r="E950" t="inlineStr">
         <is>
-          <t>https://www.saintleu.re/fiche-association/psychez-toi</t>
+          <t>https://www.saint-benoit.re/page/483-associations-de-linsertion</t>
         </is>
       </c>
       <c r="F950" t="inlineStr">
         <is>
-          <t>2023-04-24 (fiche annuaire saintleu.re, dateModified; site actif 2026)</t>
+          <t>Page mairie non datée ; site mairie actif (actualités publiées 2026-10-19, rubrique Rouge Ruelle 2026), relevé 2026-10-20</t>
         </is>
       </c>
       <c r="G950" t="inlineStr">
@@ -39371,14 +39371,14 @@
       </c>
       <c r="H950" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>site_actif_sans_date</t>
         </is>
       </c>
     </row>
     <row r="951">
       <c r="A951" t="inlineStr">
         <is>
-          <t>Respirun</t>
+          <t>Psychez Toi</t>
         </is>
       </c>
       <c r="B951" t="inlineStr">
@@ -39388,18 +39388,22 @@
       </c>
       <c r="C951" t="inlineStr">
         <is>
-          <t>contact@respirun.org</t>
-        </is>
-      </c>
-      <c r="D951" t="inlineStr"/>
+          <t>psycheztoi@gmail.com</t>
+        </is>
+      </c>
+      <c r="D951" t="inlineStr">
+        <is>
+          <t>06 93 92 04 23</t>
+        </is>
+      </c>
       <c r="E951" t="inlineStr">
         <is>
-          <t>https://www.saintleu.re/fiche-association/respirun</t>
+          <t>https://www.saintleu.re/fiche-association/psychez-toi</t>
         </is>
       </c>
       <c r="F951" t="inlineStr">
         <is>
-          <t>2023-08-04 (fiche annuaire saintleu.re, dateModified; site actif 2026)</t>
+          <t>2023-04-24 (fiche annuaire saintleu.re, dateModified; site actif 2026)</t>
         </is>
       </c>
       <c r="G951" t="inlineStr">
@@ -39416,7 +39420,7 @@
     <row r="952">
       <c r="A952" t="inlineStr">
         <is>
-          <t>Solidarité-Inter Génération</t>
+          <t>Respirun</t>
         </is>
       </c>
       <c r="B952" t="inlineStr">
@@ -39426,22 +39430,18 @@
       </c>
       <c r="C952" t="inlineStr">
         <is>
-          <t>daniel.faivre@yahoo.fr</t>
-        </is>
-      </c>
-      <c r="D952" t="inlineStr">
-        <is>
-          <t>0262 34 94 37 / 0692 23 92 49</t>
-        </is>
-      </c>
+          <t>contact@respirun.org</t>
+        </is>
+      </c>
+      <c r="D952" t="inlineStr"/>
       <c r="E952" t="inlineStr">
         <is>
-          <t>https://www.saintleu.re/fiche-association/solidarite-inter-generation</t>
+          <t>https://www.saintleu.re/fiche-association/respirun</t>
         </is>
       </c>
       <c r="F952" t="inlineStr">
         <is>
-          <t>2022-04-21 (fiche annuaire saintleu.re, dateModified; site actif 2026)</t>
+          <t>2023-08-04 (fiche annuaire saintleu.re, dateModified; site actif 2026)</t>
         </is>
       </c>
       <c r="G952" t="inlineStr">
@@ -39458,32 +39458,32 @@
     <row r="953">
       <c r="A953" t="inlineStr">
         <is>
-          <t>Association Solidarité Sainte Thérèse</t>
+          <t>Solidarité-Inter Génération</t>
         </is>
       </c>
       <c r="B953" t="inlineStr">
         <is>
-          <t>Saint-Pierre</t>
+          <t>Saint-Leu</t>
         </is>
       </c>
       <c r="C953" t="inlineStr">
         <is>
-          <t>sainte.therese410@gmail.com</t>
+          <t>daniel.faivre@yahoo.fr</t>
         </is>
       </c>
       <c r="D953" t="inlineStr">
         <is>
-          <t>06 93 90 99 79 / 02 62 91 75 79</t>
+          <t>0262 34 94 37 / 0692 23 92 49</t>
         </is>
       </c>
       <c r="E953" t="inlineStr">
         <is>
-          <t>https://www.saintpierre.re/decouvrez-saint-pierre/le-cadre-de-vie/animations-vie-associative/repas-pour-les-demunis</t>
+          <t>https://www.saintleu.re/fiche-association/solidarite-inter-generation</t>
         </is>
       </c>
       <c r="F953" t="inlineStr">
         <is>
-          <t>2023-07-07 (actualite mairie, publie le 7 juillet 2023 ; association laique)</t>
+          <t>2022-04-21 (fiche annuaire saintleu.re, dateModified; site actif 2026)</t>
         </is>
       </c>
       <c r="G953" t="inlineStr">
@@ -39500,28 +39500,32 @@
     <row r="954">
       <c r="A954" t="inlineStr">
         <is>
-          <t>Association Réunionnaise pour le Développement de l'Insertion</t>
+          <t>Association Solidarité Sainte Thérèse</t>
         </is>
       </c>
       <c r="B954" t="inlineStr">
         <is>
-          <t>Trois-Bassins</t>
+          <t>Saint-Pierre</t>
         </is>
       </c>
       <c r="C954" t="inlineStr">
         <is>
-          <t>ardireunion@gmail.com</t>
-        </is>
-      </c>
-      <c r="D954" t="inlineStr"/>
+          <t>sainte.therese410@gmail.com</t>
+        </is>
+      </c>
+      <c r="D954" t="inlineStr">
+        <is>
+          <t>06 93 90 99 79 / 02 62 91 75 79</t>
+        </is>
+      </c>
       <c r="E954" t="inlineStr">
         <is>
-          <t>https://docs.trois-bassins.re/associations/Liste-associations-3Bassins.pdf</t>
+          <t>https://www.saintpierre.re/decouvrez-saint-pierre/le-cadre-de-vie/animations-vie-associative/repas-pour-les-demunis</t>
         </is>
       </c>
       <c r="F954" t="inlineStr">
         <is>
-          <t>2023-11-21 (PDF annuaire des associations de Trois Bassins, MAJ 21/11/2023, docs.trois-bassins.re; site actif 2026)</t>
+          <t>2023-07-07 (actualite mairie, publie le 7 juillet 2023 ; association laique)</t>
         </is>
       </c>
       <c r="G954" t="inlineStr">
@@ -39538,47 +39542,85 @@
     <row r="955">
       <c r="A955" t="inlineStr">
         <is>
+          <t>Association Réunionnaise pour le Développement de l'Insertion</t>
+        </is>
+      </c>
+      <c r="B955" t="inlineStr">
+        <is>
+          <t>Trois-Bassins</t>
+        </is>
+      </c>
+      <c r="C955" t="inlineStr">
+        <is>
+          <t>ardireunion@gmail.com</t>
+        </is>
+      </c>
+      <c r="D955" t="inlineStr"/>
+      <c r="E955" t="inlineStr">
+        <is>
+          <t>https://docs.trois-bassins.re/associations/Liste-associations-3Bassins.pdf</t>
+        </is>
+      </c>
+      <c r="F955" t="inlineStr">
+        <is>
+          <t>2023-11-21 (PDF annuaire des associations de Trois Bassins, MAJ 21/11/2023, docs.trois-bassins.re; site actif 2026)</t>
+        </is>
+      </c>
+      <c r="G955" t="inlineStr">
+        <is>
+          <t>solidarite</t>
+        </is>
+      </c>
+      <c r="H955" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+    </row>
+    <row r="956">
+      <c r="A956" t="inlineStr">
+        <is>
           <t>Kfé parents</t>
         </is>
       </c>
-      <c r="B955" t="inlineStr">
+      <c r="B956" t="inlineStr">
         <is>
           <t>Trois-Bassins</t>
         </is>
       </c>
-      <c r="C955" t="inlineStr">
+      <c r="C956" t="inlineStr">
         <is>
           <t>monique.kfeparents@gmail.com</t>
         </is>
       </c>
-      <c r="D955" t="inlineStr">
+      <c r="D956" t="inlineStr">
         <is>
           <t>0262 82 42 73</t>
         </is>
       </c>
-      <c r="E955" t="inlineStr">
+      <c r="E956" t="inlineStr">
         <is>
           <t>https://docs.trois-bassins.re/associations/Liste-associations-3Bassins.pdf</t>
         </is>
       </c>
-      <c r="F955" t="inlineStr">
+      <c r="F956" t="inlineStr">
         <is>
           <t>2023-11-21 (PDF annuaire des associations de Trois Bassins, MAJ 21/11/2023, docs.trois-bassins.re; site actif 2026)</t>
         </is>
       </c>
-      <c r="G955" t="inlineStr">
+      <c r="G956" t="inlineStr">
         <is>
           <t>solidarite</t>
         </is>
       </c>
-      <c r="H955" t="inlineStr">
+      <c r="H956" t="inlineStr">
         <is>
           <t>date</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:H955"/>
+  <autoFilter ref="A1:H956"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -39853,7 +39895,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Pas d'annuaire ; page vie-associative en 404. Emails trouvés dans des arrêtés de manifestation/débit de boissons et le programme JEP publiés sur saintpierre.re (2024-2025). Écartés : Marmite Insolite (société commerciale), contacts d'agents (@saintpierre.re), Solidarité Sainte-Thérèse (déjà acquis). Quota Tavily 429 atteint ponctuellement ; les autres arrêtés (AJBS, Club Dominos Lé Margoz, Rugby Club, Run Power, Labelistic, Gaston Richardson) n'ont pas pu être lus en entier (extraction PDF échouée), emails non vérifiés donc non retenus.</t>
+          <t>802 PDF d'arrêtés de manifestations (2023-2026, tous scannés, OCR tesseract), 2173 autres PDF du site et 1487 pages analysés. Les arrêtés ne contiennent presque aucun email d'association : seuls VBSP, Saint-Pierre Handball Club (déjà acquis) et une SAS commerciale (Marmite Insolite, exclue) en ont un. Cibles sans email dans les arrêtés : Amicale des Jeunes Boulistes du Sud, Club Dominos Lé Margoz, Rugby Club Saint-Pierre et du Sud, Run Power Production, Labelistic (téléphone seul ou rien), Association Gaston Richardson (tél 06 92 87 85 73 seulement). Pages Maison Sport-Santé (OMS d'autres communes, CASEC, Ekilib) écartées : aucune date lisible sur la page. Le Vieux Domaine écarté (propriété privée, pas d'association nommée).</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
